--- a/data/trans_orig/IP07_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_R2-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8877</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>4503</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7891</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9061</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4811</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9444</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81390</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77324</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84152</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>86364</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82976</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88986</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81806</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88927</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81390</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76757</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84147</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162037</t>
+          <t>161728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171837</t>
+          <t>171805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86201</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86201</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86201</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16010</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10529</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23273</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6510</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11002</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11818</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16010</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10929</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23244</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31266</t>
+          <t>31051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>459481</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>452218</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>464962</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>618</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>409577</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>405085</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>412949</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>404269</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>413049</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>459481</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>452247</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>464562</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>860313</t>
+          <t>860528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>875696</t>
+          <t>875833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475491</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475491</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475491</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>475491</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>475491</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>475491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3173</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8840</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152877</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148256</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155484</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173434</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>170893</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>170567</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152877</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148631</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155493</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,39%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>481</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320986</t>
+          <t>321632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328998</t>
+          <t>329037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157471</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157471</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157471</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,74 +1752,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18677</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33624</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7265</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18649</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18628</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18605</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33960</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>693749</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>685539</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700486</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>669376</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>662372</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>673756</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>662393</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>674153</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>693749</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>685203</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>700558</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1353545</t>
+          <t>1353448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1372239</t>
+          <t>1371841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>719163</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>719163</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>719163</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>719163</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>719163</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>719163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,107 +2326,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2397</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5884</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5937</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2987</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10718</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10995</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2439,107 +2439,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81643</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77387</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84071</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89972</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86485</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91713</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86432</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>91721</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81643</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>77283</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83917</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>171614</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>167003</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>174734</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>98,32%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>171614</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>166726</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>174990</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12777</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8175</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19764</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12664</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19703</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7272</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19066</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12777</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8137</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19846</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>478847</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>471860</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>483449</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>438112</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>431073</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>443257</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>431710</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>443504</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>478847</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471778</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>483487</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907754</t>
+          <t>908684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>924209</t>
+          <t>923893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>491624</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>491624</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>491624</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>653</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>450776</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>450776</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>450776</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>491624</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>491624</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>491624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2240</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5754</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>169988</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>165091</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164468</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160587</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>161203</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>169988</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>166474</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171589</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>474</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329630</t>
+          <t>329035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336958</t>
+          <t>336809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12455</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26109</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10563</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24280</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10857</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24748</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12934</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26451</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45871</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>730479</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>723096</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>736750</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>998</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>692551</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>698607</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>684422</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>698313</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>730479</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>722754</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>736271</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1412504</t>
+          <t>1411747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1431755</t>
+          <t>1431173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>749205</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>749205</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>749205</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>709170</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>749205</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>749205</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>749205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2205</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>531</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6264</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5431</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66594</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63177</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67990</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57173</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53114</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>53473</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>58847</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66594</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63183</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67981</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118853</t>
+          <t>119015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126201</t>
+          <t>126426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6838</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10121</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5892</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16322</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5746</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16194</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11375</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6777</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18247</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29933</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475186</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>468308</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>479723</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>694</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>458872</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>452671</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>463101</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>452799</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>463247</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475186</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>468314</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>479784</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>925621</t>
+          <t>925608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941044</t>
+          <t>940664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486561</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486561</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486561</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>468993</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>468993</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>468993</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486561</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486561</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5950</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1073</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5790</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>184746</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>180899</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186255</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>170329</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167968</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>168042</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>171402</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>184746</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>181059</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186254</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>521</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350665</t>
+          <t>351267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357106</t>
+          <t>357216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>171402</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>171402</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>171402</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23187</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8737</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21336</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8496</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20805</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9417</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22821</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>37817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>726525</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>718837</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>732440</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>686375</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>678437</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>691036</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>691277</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>726525</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>719203</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>732607</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1403464</t>
+          <t>1403980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1420876</t>
+          <t>1420256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>699773</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8704</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6953</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23974</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48028</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55068</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47725</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30704</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54222</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>44938</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>46411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>105004</t>
+          <t>97413</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89809</t>
+          <t>92412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111907</t>
+          <t>100654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7609</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3979</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13908</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11631</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6575</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18831</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>468069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>461770</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>471699</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>448879</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>441679</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>453935</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>508202</t>
+          <t>420839</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500947</t>
+          <t>414019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512076</t>
+          <t>425977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>957081</t>
+          <t>888908</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948178</t>
+          <t>879248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963546</t>
+          <t>895341</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12147</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7064</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7967</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5527</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12163</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163155</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156272</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166274</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>146991</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>142487</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148747</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>147264</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>142009</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149171</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>177822</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>171186</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181069</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>459</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>324813</t>
+          <t>310419</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317963</t>
+          <t>303073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329152</t>
+          <t>314669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25332</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12859</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43533</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28183</t>
+          <t>24787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>683698</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>675497</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>690065</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>643594</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>621205</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>651879</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>743303</t>
+          <t>613042</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734417</t>
+          <t>604781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>750007</t>
+          <t>619115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1386897</t>
+          <t>1296740</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1364955</t>
+          <t>1285701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1398527</t>
+          <t>1305224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
